--- a/restaurant_evaluation_forms/015_favorite_dishes_feedback_form--restaurant_evaluation_forms.xlsx
+++ b/restaurant_evaluation_forms/015_favorite_dishes_feedback_form--restaurant_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -650,8 +650,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,12 +679,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'appetizers'}</t>
+          <t>appetizers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Appetizers'}</t>
+          <t>Appetizers</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'entrees'}</t>
+          <t>entrees</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Entrees'}</t>
+          <t>Entrees</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'desserts'}</t>
+          <t>desserts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Desserts'}</t>
+          <t>Desserts</t>
         </is>
       </c>
     </row>
